--- a/tame_output/ON/bt/strategyON_20240320.xlsx
+++ b/tame_output/ON/bt/strategyON_20240320.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-62.0%</t>
+          <t>-61.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-55.3%</t>
+          <t>-55.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-364.6%</t>
+          <t>-364.4%</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-153.9%</t>
+          <t>-153.8%</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-68.7%</t>
+          <t>-68.5%</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>84.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-49.1%</t>
         </is>
       </c>
     </row>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309728</v>
+        <v>3.83324917230973</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860426</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.381231958457676</v>
+        <v>3.381231958457678</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-2.030420479277076</v>
+        <v>-2.02837913478158</v>
       </c>
       <c r="E1908" t="n">
-        <v>2.223553800561858</v>
+        <v>2.224370338360057</v>
       </c>
       <c r="F1908" t="n">
-        <v>1.552731986718319</v>
+        <v>1.554773331213815</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.967717608617428</v>
+        <v>3.968942415314725</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240320.xlsx
+++ b/tame_output/ON/bt/strategyON_20240320.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-61.9%</t>
+          <t>-62.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>100.2%</t>
+          <t>100.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-55.2%</t>
+          <t>-55.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>497.4%</t>
+          <t>497.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-364.4%</t>
+          <t>-366.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-153.8%</t>
+          <t>-154.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-248.1%</t>
+          <t>-244.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>814.0%</t>
+          <t>-510.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>-521.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-68.5%</t>
+          <t>-66.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-149.2%</t>
+          <t>-147.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-47.9%</t>
         </is>
       </c>
     </row>
@@ -44061,10 +44061,10 @@
         <v>2.947546866034124</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.412918451291926</v>
+        <v>1.450444584979295</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.964697737325107</v>
+        <v>3.987213417537529</v>
       </c>
     </row>
     <row r="1849">
@@ -44084,10 +44084,10 @@
         <v>2.869237387246818</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.412918451291926</v>
+        <v>1.450444584979295</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.969589881879032</v>
+        <v>3.992105562091454</v>
       </c>
     </row>
     <row r="1850">
@@ -44107,10 +44107,10 @@
         <v>2.756158858501252</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.14251848858304</v>
+        <v>1.18004462227041</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.802431360591689</v>
+        <v>3.824947040804111</v>
       </c>
     </row>
     <row r="1851">
@@ -44130,10 +44130,10 @@
         <v>2.746589188808929</v>
       </c>
       <c r="F1851" t="n">
-        <v>1.13588356608611</v>
+        <v>1.173409699773479</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.79153470639998</v>
+        <v>3.814050386612402</v>
       </c>
     </row>
     <row r="1852">
@@ -44153,10 +44153,10 @@
         <v>2.635720589856705</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.807866344358631</v>
+        <v>0.8453924780460002</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.615062663102261</v>
+        <v>3.637578343314682</v>
       </c>
     </row>
     <row r="1853">
@@ -44176,10 +44176,10 @@
         <v>2.645154038868863</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.8105583767776624</v>
+        <v>0.8480845104650315</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.624776632962248</v>
+        <v>3.64729231317467</v>
       </c>
     </row>
     <row r="1854">
@@ -44199,10 +44199,10 @@
         <v>2.499576010245976</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.4438473251111168</v>
+        <v>0.4813734587984859</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.405856394006053</v>
+        <v>3.428372074218474</v>
       </c>
     </row>
     <row r="1855">
@@ -44222,10 +44222,10 @@
         <v>2.497946269439401</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.4438473251111168</v>
+        <v>0.4813734587984859</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.404398932818916</v>
+        <v>3.426914613031338</v>
       </c>
     </row>
     <row r="1856">
@@ -44245,10 +44245,10 @@
         <v>2.362242283603353</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.3359412730838986</v>
+        <v>0.3734674067712677</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.341424425057201</v>
+        <v>3.363940105269623</v>
       </c>
     </row>
     <row r="1857">
@@ -44268,10 +44268,10 @@
         <v>2.215288202164271</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.02170907715444953</v>
+        <v>0.01581705653291959</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.122940273570451</v>
+        <v>3.145455953782872</v>
       </c>
     </row>
     <row r="1858">
@@ -44291,10 +44291,10 @@
         <v>2.214396752775671</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.02170907715444953</v>
+        <v>0.01581705653291959</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.12471320027071</v>
+        <v>3.147228880483131</v>
       </c>
     </row>
     <row r="1859">
@@ -44314,10 +44314,10 @@
         <v>2.028007322983161</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.1581265735957165</v>
+        <v>-0.1206004399083474</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.029195589873354</v>
+        <v>3.051711270085776</v>
       </c>
     </row>
     <row r="1860">
@@ -44337,10 +44337,10 @@
         <v>1.885719086438154</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.2405948241028647</v>
+        <v>-0.2030686904154956</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.967999414571156</v>
+        <v>2.990515094783577</v>
       </c>
     </row>
     <row r="1861">
@@ -44360,10 +44360,10 @@
         <v>1.883674017649998</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.2405948241028647</v>
+        <v>-0.2030686904154956</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.966580006227121</v>
+        <v>2.989095686439542</v>
       </c>
     </row>
     <row r="1862">
@@ -44383,10 +44383,10 @@
         <v>1.744711079924114</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3388164609699905</v>
+        <v>-0.3012903272826214</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.914134584341087</v>
+        <v>2.936650264553509</v>
       </c>
     </row>
     <row r="1863">
@@ -44406,10 +44406,10 @@
         <v>1.744936420741433</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.3391492427771421</v>
+        <v>-0.301623109089773</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.913189430262628</v>
+        <v>2.935705110475049</v>
       </c>
     </row>
     <row r="1864">
@@ -44429,10 +44429,10 @@
         <v>1.580262453883921</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.7477380199578205</v>
+        <v>-0.7102118862704514</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.66679770796898</v>
+        <v>2.689313388181401</v>
       </c>
     </row>
     <row r="1865">
@@ -44452,10 +44452,10 @@
         <v>1.410254892698944</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.7477380199578205</v>
+        <v>-0.7102118862704514</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.66198314044044</v>
+        <v>2.684498820652862</v>
       </c>
     </row>
     <row r="1866">
@@ -44475,10 +44475,10 @@
         <v>1.241692193593022</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.7477380199578205</v>
+        <v>-0.7102118862704514</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.659977191049318</v>
+        <v>2.682492871261739</v>
       </c>
     </row>
     <row r="1867">
@@ -44498,10 +44498,10 @@
         <v>1.101280080049763</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.7477380199578205</v>
+        <v>-0.7102118862704514</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.670235881717997</v>
+        <v>2.692751561930418</v>
       </c>
     </row>
     <row r="1868">
@@ -44521,10 +44521,10 @@
         <v>1.091893699465414</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.7477380199578205</v>
+        <v>-0.7102118862704514</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.666335446863692</v>
+        <v>2.688851127076113</v>
       </c>
     </row>
     <row r="1869">
@@ -44544,10 +44544,10 @@
         <v>0.9651686998224234</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.7477380199578205</v>
+        <v>-0.7102118862704514</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.664740366918693</v>
+        <v>2.687256047131114</v>
       </c>
     </row>
     <row r="1870">
@@ -44567,10 +44567,10 @@
         <v>0.9670224603654964</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.7492846546606063</v>
+        <v>-0.7117585209732372</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.667591362026229</v>
+        <v>2.690107042238651</v>
       </c>
     </row>
     <row r="1871">
@@ -44590,10 +44590,10 @@
         <v>0.789656512586999</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.7492846546606063</v>
+        <v>-0.7117585209732372</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.663565057491826</v>
+        <v>2.686080737704248</v>
       </c>
     </row>
     <row r="1872">
@@ -44613,10 +44613,10 @@
         <v>0.6363538557683626</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.7492846546606063</v>
+        <v>-0.7117585209732372</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.663462956170242</v>
+        <v>2.685978636382664</v>
       </c>
     </row>
     <row r="1873">
@@ -44636,10 +44636,10 @@
         <v>0.4889312412712816</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.124269980831884</v>
+        <v>-1.086743847144515</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.441043276438906</v>
+        <v>2.463558956651327</v>
       </c>
     </row>
     <row r="1874">
@@ -44659,10 +44659,10 @@
         <v>0.3504694155677313</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.124269980831884</v>
+        <v>-1.086743847144515</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.446393579736956</v>
+        <v>2.468909259949378</v>
       </c>
     </row>
     <row r="1875">
@@ -44682,10 +44682,10 @@
         <v>0.2278254240589033</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.450670009496897</v>
+        <v>-1.413143875809528</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.258469582495126</v>
+        <v>2.280985262707548</v>
       </c>
     </row>
     <row r="1876">
@@ -44705,10 +44705,10 @@
         <v>0.2334576333980962</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.444193862703337</v>
+        <v>-1.406667729015968</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.265397021193031</v>
+        <v>2.287912701405452</v>
       </c>
     </row>
     <row r="1877">
@@ -44728,10 +44728,10 @@
         <v>0.2349340033806606</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.444193862703337</v>
+        <v>-1.406667729015968</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.265397021193031</v>
+        <v>2.287912701405452</v>
       </c>
     </row>
     <row r="1878">
@@ -44751,10 +44751,10 @@
         <v>0.2433333416480297</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.374415627412955</v>
+        <v>-1.336889493725586</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.312777159485902</v>
+        <v>2.335292839698323</v>
       </c>
     </row>
     <row r="1879">
@@ -44774,10 +44774,10 @@
         <v>0.268227034565196</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.299206289105854</v>
+        <v>-1.261680155418485</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.362385316954599</v>
+        <v>2.38490099716702</v>
       </c>
     </row>
     <row r="1880">
@@ -44797,10 +44797,10 @@
         <v>0.3129866687255962</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.225736457438406</v>
+        <v>-1.188210323751037</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.421838917448489</v>
+        <v>2.44435459766091</v>
       </c>
     </row>
     <row r="1881">
@@ -44820,10 +44820,10 @@
         <v>0.3596908316586851</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.145364101974476</v>
+        <v>-1.107837968287107</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.484617551474363</v>
+        <v>2.507133231686785</v>
       </c>
     </row>
     <row r="1882">
@@ -44843,10 +44843,10 @@
         <v>0.2771625458107514</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.145364101974476</v>
+        <v>-1.107837968287107</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.477398386572768</v>
+        <v>2.499914066785188</v>
       </c>
     </row>
     <row r="1883">
@@ -44866,10 +44866,10 @@
         <v>0.2624244984169564</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.165528743524024</v>
+        <v>-1.128002609836655</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.458627410869063</v>
+        <v>2.481143091081484</v>
       </c>
     </row>
     <row r="1884">
@@ -44889,10 +44889,10 @@
         <v>0.1716105093899829</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.328176280594184</v>
+        <v>-1.290650146906815</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.362154678465523</v>
+        <v>2.384670358677944</v>
       </c>
     </row>
     <row r="1885">
@@ -44912,10 +44912,10 @@
         <v>0.199531930941633</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.356689843276418</v>
+        <v>-1.319163709589049</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.347740269485297</v>
+        <v>2.370255949697718</v>
       </c>
     </row>
     <row r="1886">
@@ -44935,10 +44935,10 @@
         <v>0.224328472215559</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.356689843276418</v>
+        <v>-1.319163709589049</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.351730605171698</v>
+        <v>2.374246285384119</v>
       </c>
     </row>
     <row r="1887">
@@ -44958,10 +44958,10 @@
         <v>0.1903364734951354</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.356689843276418</v>
+        <v>-1.319163709589049</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.350255378272956</v>
+        <v>2.372771058485378</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44981,10 +44981,10 @@
         <v>0.2842976459512068</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.15942043754842</v>
+        <v>-1.121894303861051</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.483670431874627</v>
+        <v>2.506186112087049</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45004,10 +45004,10 @@
         <v>0.3509073551993636</v>
       </c>
       <c r="F1889" t="n">
-        <v>-0.9940979115986067</v>
+        <v>-0.9565717779112378</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.569812813797832</v>
+        <v>2.592328494010253</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45027,10 +45027,10 @@
         <v>0.4508244893233364</v>
       </c>
       <c r="F1890" t="n">
-        <v>-0.952171236011443</v>
+        <v>-0.9146451023240741</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.604547892186339</v>
+        <v>2.627063572398761</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45050,10 +45050,10 @@
         <v>0.5664735588084731</v>
       </c>
       <c r="F1891" t="n">
-        <v>-0.952171236011443</v>
+        <v>-0.9146451023240741</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.605687036742398</v>
+        <v>2.628202716954819</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45073,10 +45073,10 @@
         <v>0.6598256637999143</v>
       </c>
       <c r="F1892" t="n">
-        <v>-0.8840572913898985</v>
+        <v>-0.8465311577025296</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.649189177677433</v>
+        <v>2.671704857889853</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45096,10 +45096,10 @@
         <v>0.77912286041005</v>
       </c>
       <c r="F1893" t="n">
-        <v>-0.8840572913898985</v>
+        <v>-0.8465311577025296</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.654922881916069</v>
+        <v>2.67743856212849</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45119,10 +45119,10 @@
         <v>0.8681804980933658</v>
       </c>
       <c r="F1894" t="n">
-        <v>-0.6370700411969464</v>
+        <v>-0.5995439075095775</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.793377969637975</v>
+        <v>2.815893649850396</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702413</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45142,10 +45142,10 @@
         <v>0.9638317636620859</v>
       </c>
       <c r="F1895" t="n">
-        <v>-0.6370700411969464</v>
+        <v>-0.5995439075095775</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.783494488325067</v>
+        <v>2.806010168537489</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45165,10 +45165,10 @@
         <v>1.068893923510071</v>
       </c>
       <c r="F1896" t="n">
-        <v>-0.6370700411969464</v>
+        <v>-0.5995439075095775</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.781659927825693</v>
+        <v>2.804175608038115</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45188,10 +45188,10 @@
         <v>1.178917273896804</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.5480507329182129</v>
+        <v>-0.510524599230844</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.834771197819473</v>
+        <v>2.857286878031894</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45211,10 +45211,10 @@
         <v>1.287212815149089</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.2789831451512336</v>
+        <v>-0.2414570114638647</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.996880256625154</v>
+        <v>3.019395936837575</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45234,10 +45234,10 @@
         <v>1.379576474316456</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.0149232068284374</v>
+        <v>0.0226029268589315</v>
       </c>
       <c r="G1899" t="n">
-        <v>3.14205590345708</v>
+        <v>3.164571583669501</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83324917230973</v>
+        <v>3.833249172309728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45257,10 +45257,10 @@
         <v>1.65962129005809</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.0149232068284374</v>
+        <v>0.0226029268589315</v>
       </c>
       <c r="G1900" t="n">
-        <v>3.139268869796779</v>
+        <v>3.1617845500092</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45280,10 +45280,10 @@
         <v>1.759821325940312</v>
       </c>
       <c r="F1901" t="n">
-        <v>0.2347178231575143</v>
+        <v>0.2722439568448832</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.289397111676191</v>
+        <v>3.311912791888612</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45303,10 +45303,10 @@
         <v>1.861004906897499</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.4892597224985898</v>
+        <v>0.5267858561859587</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.441489072501593</v>
+        <v>3.464004752714015</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45326,10 +45326,10 @@
         <v>1.962321824627191</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.7227409447281884</v>
+        <v>0.7602670784155573</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.589502234677205</v>
+        <v>3.612017914889626</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45349,10 +45349,10 @@
         <v>2.03131302637178</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.7799124488908845</v>
+        <v>0.8174385825782534</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.620912926861863</v>
+        <v>3.643428607074285</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.763178672860426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45372,10 +45372,10 @@
         <v>2.079590702571163</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.9121879225217712</v>
+        <v>0.9497140562091401</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.695645697787422</v>
+        <v>3.718161377999844</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45395,10 +45395,10 @@
         <v>2.15864563312806</v>
       </c>
       <c r="F1906" t="n">
-        <v>1.102787597194924</v>
+        <v>1.140313730882293</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.812820563278951</v>
+        <v>3.835336243491372</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45418,10 +45418,10 @@
         <v>2.271151893825151</v>
       </c>
       <c r="F1907" t="n">
-        <v>1.351787395878504</v>
+        <v>1.389313529565873</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.975126783712758</v>
+        <v>3.997642463925179</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.381231958457678</v>
+        <v>3.382635807901503</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-2.02837913478158</v>
+        <v>-2.04526497075575</v>
       </c>
       <c r="E1908" t="n">
-        <v>2.224370338360057</v>
+        <v>2.217616003970389</v>
       </c>
       <c r="F1908" t="n">
-        <v>1.554773331213815</v>
+        <v>1.575413628927015</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.968942415314725</v>
+        <v>3.981326593942645</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240320.xlsx
+++ b/tame_output/ON/bt/strategyON_20240320.xlsx
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>100.1%</t>
+          <t>100.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-366.1%</t>
+          <t>-365.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-154.5%</t>
+          <t>-154.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-66.5%</t>
+          <t>-65.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-47.6%</t>
         </is>
       </c>
     </row>
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-2.04526497075575</v>
+        <v>-2.039985995255951</v>
       </c>
       <c r="E1908" t="n">
-        <v>2.217616003970389</v>
+        <v>2.219727594170308</v>
       </c>
       <c r="F1908" t="n">
-        <v>1.575413628927015</v>
+        <v>1.580692604426813</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.981326593942645</v>
+        <v>3.984493979242525</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240320.xlsx
+++ b/tame_output/ON/bt/strategyON_20240320.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>8.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-35.3%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-8.5%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-63.8%</t>
+          <t>-62.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>115.8%</t>
+          <t>114.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-478.0%</t>
+          <t>-468.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-57.1%</t>
+          <t>-55.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>82.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>504.8%</t>
+          <t>497.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-387.6%</t>
+          <t>-367.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-191.6%</t>
+          <t>-187.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-185.3%</t>
+          <t>-155.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-257.9%</t>
+          <t>-248.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-118.6%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-98.7%</t>
+          <t>-90.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-155.1%</t>
+          <t>-149.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-89.5%</t>
+          <t>-62.9%</t>
         </is>
       </c>
     </row>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.9994340999919192</v>
+        <v>-0.9038271302363685</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.71679020313135</v>
+        <v>2.75503299103357</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.044096850158285</v>
+        <v>1.139703819913836</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.743378377536836</v>
+        <v>3.800742559390166</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.006069022488849</v>
+        <v>-0.9104620527332987</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.707220533439027</v>
+        <v>2.745463321341247</v>
       </c>
       <c r="F1851" t="n">
-        <v>1.037461927661355</v>
+        <v>1.133068897416906</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.732481723345127</v>
+        <v>3.789845905198457</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.334086244216328</v>
+        <v>-1.238479274460778</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.596351934486803</v>
+        <v>2.634594722389024</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.7094447059338759</v>
+        <v>0.8050516756894265</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.556009680047408</v>
+        <v>3.613373861900738</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.330749497707357</v>
+        <v>-1.235142527951806</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.605785383498961</v>
+        <v>2.644028171401181</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.7121367383529073</v>
+        <v>0.8077437081084579</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.565723649907395</v>
+        <v>3.623087831760726</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.697460549373903</v>
+        <v>-1.601853579618352</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.460207354876074</v>
+        <v>2.498450142778295</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.3454256866863616</v>
+        <v>0.4410326564419123</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.3468034109512</v>
+        <v>3.40416759280453</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-1.697891248422498</v>
+        <v>-1.602284278666947</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.458577614069499</v>
+        <v>2.49682040197172</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.3454256866863616</v>
+        <v>0.4410326564419123</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.345345949764063</v>
+        <v>3.402710131617393</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.04157402164916</v>
+        <v>-1.94596705189361</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.322873628233451</v>
+        <v>2.361116416135671</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.2375196346591434</v>
+        <v>0.333126604414694</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.282371442002348</v>
+        <v>3.339735623855679</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-2.399224371887509</v>
+        <v>-2.303617402131958</v>
       </c>
       <c r="E1857" t="n">
-        <v>2.175919546794369</v>
+        <v>2.21416233469659</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.1201307155792047</v>
+        <v>-0.02452374582365408</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.063887290515597</v>
+        <v>3.121251472368928</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-2.405885312109656</v>
+        <v>-2.310278342354106</v>
       </c>
       <c r="E1858" t="n">
-        <v>2.175028097405769</v>
+        <v>2.21327088530799</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.1201307155792047</v>
+        <v>-0.02452374582365408</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.065660217215857</v>
+        <v>3.123024399069187</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-2.837691105259444</v>
+        <v>-2.742084135503894</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.988638667613259</v>
+        <v>2.026881455515479</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.2565482120204717</v>
+        <v>-0.1609412422649211</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.970142606818501</v>
+        <v>3.027506788671832</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.164123634127188</v>
+        <v>-3.068516664371637</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.846350431068252</v>
+        <v>1.884593218970472</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3390164625276199</v>
+        <v>-0.2434094927720692</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.908946431516303</v>
+        <v>2.966310613369633</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.165687785237491</v>
+        <v>-3.07008081548194</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.844305362280096</v>
+        <v>1.882548150182316</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.3390164625276199</v>
+        <v>-0.2434094927720692</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.907527023172268</v>
+        <v>2.964891205025598</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-3.529314030137804</v>
+        <v>-3.433707060382253</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.705342424554212</v>
+        <v>1.743585212456433</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.4372380993947457</v>
+        <v>-0.3416311296391951</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.855081601286234</v>
+        <v>2.912445783139564</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-3.526886965609085</v>
+        <v>-3.431279995853535</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.705567765371531</v>
+        <v>1.743810553273751</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.4375708812018973</v>
+        <v>-0.3419639114463467</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.854136447207774</v>
+        <v>2.911500629061105</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-3.935475742789764</v>
+        <v>-3.839868773034213</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.540893798514019</v>
+        <v>1.579136586416239</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.8461596583825757</v>
+        <v>-0.7505526886270251</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.607744724914126</v>
+        <v>2.665108906767457</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.348458226930857</v>
+        <v>-4.252851257175307</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.370886237329042</v>
+        <v>1.409129025231262</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.8461596583825757</v>
+        <v>-0.7505526886270251</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.602930157385587</v>
+        <v>2.660294339238917</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-4.764850101217855</v>
+        <v>-4.669243131462304</v>
       </c>
       <c r="E1866" t="n">
-        <v>1.20232353822312</v>
+        <v>1.24056632612534</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.8461596583825757</v>
+        <v>-0.7505526886270251</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.600924207994464</v>
+        <v>2.658288389847795</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.141527111747699</v>
+        <v>-5.045920141992148</v>
       </c>
       <c r="E1867" t="n">
-        <v>1.061911424679861</v>
+        <v>1.100154212582082</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.8461596583825757</v>
+        <v>-0.7505526886270251</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.611182898663143</v>
+        <v>2.668547080516474</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.15524197607281</v>
+        <v>-5.05963500631726</v>
       </c>
       <c r="E1868" t="n">
-        <v>1.052525044095512</v>
+        <v>1.090767831997733</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.8461596583825757</v>
+        <v>-0.7505526886270251</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.607282463808839</v>
+        <v>2.664646645662169</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-5.46806677531779</v>
+        <v>-5.372459805562239</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.9258000444525214</v>
+        <v>0.9640428323547416</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.8461596583825757</v>
+        <v>-0.7505526886270251</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.60568738386384</v>
+        <v>2.66305156571717</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969597</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-5.472879813783127</v>
+        <v>-5.377272844027576</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.9276538049955945</v>
+        <v>0.9658965928978147</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.8477062930853615</v>
+        <v>-0.7520993233298109</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.608538378971376</v>
+        <v>2.665902560824707</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-5.906228921893363</v>
+        <v>-5.810621952137812</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.750287857217097</v>
+        <v>0.7885306451193173</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.8477062930853615</v>
+        <v>-0.7520993233298109</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.604512074436973</v>
+        <v>2.661876256290304</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.289230310635994</v>
+        <v>-6.193623340880444</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.5969852003984606</v>
+        <v>0.6352279883006808</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.8477062930853615</v>
+        <v>-0.7520993233298109</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.604409973115389</v>
+        <v>2.661774154968719</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-6.664215636807271</v>
+        <v>-6.568608667051721</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.4495625859013797</v>
+        <v>0.4878053738035999</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.222691619256639</v>
+        <v>-1.127084649501088</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.381990293384053</v>
+        <v>2.439354475237383</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.023745959311273</v>
+        <v>-6.928138989555722</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.3111007601978293</v>
+        <v>0.3493435481000495</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.222691619256639</v>
+        <v>-1.127084649501088</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.387340596682103</v>
+        <v>2.444704778535433</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.350145987976286</v>
+        <v>-7.254539018220735</v>
       </c>
       <c r="E1875" t="n">
-        <v>0.1884567686890013</v>
+        <v>0.2266995565912215</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.549091647921652</v>
+        <v>-1.453484678166101</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.199416599440273</v>
+        <v>2.256780781293603</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.343669841182726</v>
+        <v>-7.248062871427176</v>
       </c>
       <c r="E1876" t="n">
-        <v>0.1940889780281942</v>
+        <v>0.2323317659304145</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.542615501128092</v>
+        <v>-1.447008531372542</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.206344038138177</v>
+        <v>2.263708219991508</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.339978916226315</v>
+        <v>-7.244371946470764</v>
       </c>
       <c r="E1877" t="n">
-        <v>0.1955653480107586</v>
+        <v>0.2338081359129789</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.542615501128092</v>
+        <v>-1.447008531372542</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.206344038138177</v>
+        <v>2.263708219991508</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-7.332763563354499</v>
+        <v>-7.237156593598948</v>
       </c>
       <c r="E1878" t="n">
-        <v>0.2039646862781277</v>
+        <v>0.2422074741803479</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.472837265837711</v>
+        <v>-1.37723029608216</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.253724176431048</v>
+        <v>2.311088358284379</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-7.281735717272673</v>
+        <v>-7.186128747517122</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.2288583791952941</v>
+        <v>0.2671011670975143</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.39762792753061</v>
+        <v>-1.302020957775059</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.303332333899745</v>
+        <v>2.360696515753076</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-7.208265885605225</v>
+        <v>-7.112658915849674</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.2736180133556942</v>
+        <v>0.3118608012579145</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.324158095863161</v>
+        <v>-1.228551126107611</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.362785934393635</v>
+        <v>2.420150116246966</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-7.127893530141295</v>
+        <v>-7.032286560385744</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.3203221762887831</v>
+        <v>0.3585649641910034</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.243785740399232</v>
+        <v>-1.148178770643681</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.42556456841951</v>
+        <v>2.482928750272841</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880266</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-7.316166332507139</v>
+        <v>-7.220559362751588</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.2377938904408494</v>
+        <v>0.2760366783430697</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.243785740399232</v>
+        <v>-1.148178770643681</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.418345403517914</v>
+        <v>2.475709585371245</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234391</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-7.336330974056686</v>
+        <v>-7.240724004301136</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.2230558430470544</v>
+        <v>0.2612986309492746</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.263950381948779</v>
+        <v>-1.168343412193228</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.399574427814209</v>
+        <v>2.45693860966754</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860581</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-7.566155421220511</v>
+        <v>-7.47054845146496</v>
       </c>
       <c r="E1884" t="n">
-        <v>0.1322418540200809</v>
+        <v>0.1704846419223012</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.426597919018939</v>
+        <v>-1.330990949263389</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.30310169541067</v>
+        <v>2.360465877264</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767394</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-7.503086188914172</v>
+        <v>-7.407479219158621</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.160163275571731</v>
+        <v>0.1984060634739513</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.455111481701174</v>
+        <v>-1.359504511945623</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.288687286430444</v>
+        <v>2.346051468283774</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792538</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-7.45107067494536</v>
+        <v>-7.355463705189809</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.184959816845657</v>
+        <v>0.2232026047478772</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.455111481701174</v>
+        <v>-1.359504511945623</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.292677622116845</v>
+        <v>2.350041803970175</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628915</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-7.532362604499564</v>
+        <v>-7.436755634744014</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.1509678181252334</v>
+        <v>0.1892106060274537</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.455111481701174</v>
+        <v>-1.359504511945623</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.291202395218103</v>
+        <v>2.348566577071433</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410713</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-7.527254418478793</v>
+        <v>-7.239486229016015</v>
       </c>
       <c r="E1888" t="n">
-        <v>0.1680645026984142</v>
+        <v>0.283171778483525</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.450003295680403</v>
+        <v>-1.162235106217625</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.309320716995438</v>
+        <v>2.481981630673104</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240573</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-7.328102311241694</v>
+        <v>-7.303880533921625</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.2346742119465706</v>
+        <v>0.2443629228745983</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.284680769730589</v>
+        <v>-1.205299422363086</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.395463098918643</v>
+        <v>2.443091907339145</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085276</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-7.102257158522283</v>
+        <v>-7.078035381202214</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.3345913460705439</v>
+        <v>0.3442800569985716</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.242754094143426</v>
+        <v>-1.163372746775923</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.43019817730715</v>
+        <v>2.477826985727651</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-6.815982346199589</v>
+        <v>-6.79176056887952</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.4502404155556801</v>
+        <v>0.4599291264837082</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.242754094143426</v>
+        <v>-1.163372746775923</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.431337321863209</v>
+        <v>2.47896613028371</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-6.589186519126256</v>
+        <v>-6.564964741806185</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.5435925205471213</v>
+        <v>0.5532812314751494</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.174640149521881</v>
+        <v>-1.095258802154378</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.474839462798243</v>
+        <v>2.522468271218745</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-6.305277788197507</v>
+        <v>-6.281056010877436</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.6628897171572574</v>
+        <v>0.6725784280852856</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.174640149521881</v>
+        <v>-1.095258802154378</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.480573167036879</v>
+        <v>2.528201975457381</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.058290538004554</v>
+        <v>-6.034068760684484</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.7519473548405733</v>
+        <v>0.7616360657686014</v>
       </c>
       <c r="F1894" t="n">
-        <v>-0.9276528993289291</v>
+        <v>-0.8482715519614258</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.619028254758785</v>
+        <v>2.666657063179287</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-5.794453670800485</v>
+        <v>-5.770231893480415</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.8475986204092933</v>
+        <v>0.8572873313373215</v>
       </c>
       <c r="F1895" t="n">
-        <v>-0.9276528993289291</v>
+        <v>-0.8482715519614258</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.609144773445878</v>
+        <v>2.65677358186638</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-5.527211869932088</v>
+        <v>-5.502990092612018</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.9526607802572782</v>
+        <v>0.9623494911853063</v>
       </c>
       <c r="F1896" t="n">
-        <v>-0.9276528993289291</v>
+        <v>-0.8482715519614258</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.607310212946504</v>
+        <v>2.654939021367006</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-5.251402706531604</v>
+        <v>-5.227180929211534</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.062684130644011</v>
+        <v>1.072372841572039</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.8386335910501956</v>
+        <v>-0.7592522436826923</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.660421482940283</v>
+        <v>2.708050291360785</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-4.982335118764625</v>
+        <v>-4.958113341444554</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.170979671896296</v>
+        <v>1.180668382824325</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.5695660032832163</v>
+        <v>-0.4901846559157129</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.822530541745965</v>
+        <v>2.870159350166467</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-4.718275180441829</v>
+        <v>-4.694053403121758</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.263343331063663</v>
+        <v>1.273032041991691</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.3055060649604201</v>
+        <v>-0.2261247175929167</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.96770618857789</v>
+        <v>3.015334996998392</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.011195556936991</v>
+        <v>-3.986973779616921</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.543388146805297</v>
+        <v>1.553076857733325</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.3055060649604201</v>
+        <v>-0.2261247175929167</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.964919154917589</v>
+        <v>3.012547963338091</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-3.761554526951039</v>
+        <v>-3.737332749630969</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.643588182687519</v>
+        <v>1.653276893615547</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.05586503497446837</v>
+        <v>0.02351631239303498</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.115047396797002</v>
+        <v>3.162676205217504</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-3.507012627609963</v>
+        <v>-3.482790850289894</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.744771763644706</v>
+        <v>1.754460474572734</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.1986768643666071</v>
+        <v>0.2780582117341105</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.267139357622404</v>
+        <v>3.314768166042906</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-3.273531405380365</v>
+        <v>-3.249309628060295</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.846088681374398</v>
+        <v>1.855777392302426</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.4321580865962057</v>
+        <v>0.511539433963709</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.415152519798015</v>
+        <v>3.462781328218517</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-3.093822875236492</v>
+        <v>-3.069601097916423</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.915079883118988</v>
+        <v>1.924768594047016</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.4893295907589018</v>
+        <v>0.5687109381264052</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.446563211982674</v>
+        <v>3.494192020403176</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-2.961547401605605</v>
+        <v>-2.937325624285536</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.96335755931837</v>
+        <v>1.973046270246398</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.6216050643897885</v>
+        <v>0.7009864117572918</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.521295982908233</v>
+        <v>3.568924791328735</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-2.770947726932453</v>
+        <v>-2.746725949612383</v>
       </c>
       <c r="E1906" t="n">
-        <v>2.042412489875268</v>
+        <v>2.052101200803295</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.8122047390629413</v>
+        <v>0.8915860864304447</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.638470848399761</v>
+        <v>3.686099656820264</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-2.521947928248872</v>
+        <v>-2.497726150928802</v>
       </c>
       <c r="E1907" t="n">
-        <v>2.154918750572358</v>
+        <v>2.164607461500387</v>
       </c>
       <c r="F1907" t="n">
-        <v>1.061204537746522</v>
+        <v>1.140585885114025</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.800777068833568</v>
+        <v>3.84840587725407</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-2.330568853387932</v>
+        <v>-2.306347076067862</v>
       </c>
       <c r="E1908" t="n">
-        <v>2.103494450917516</v>
+        <v>2.113183161845544</v>
       </c>
       <c r="F1908" t="n">
-        <v>1.252583612607462</v>
+        <v>1.331964959974965</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.787628584150914</v>
+        <v>3.835257392571416</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.702163366195154</v>
+        <v>3.365087491675547</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.813465236162626</v>
+        <v>3.031767974401426</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.259857731017965</v>
+        <v>-2.058920899523224</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.909165719441692</v>
+        <v>2.207843190278389</v>
       </c>
       <c r="F1909" t="n">
-        <v>1.252583612607462</v>
+        <v>1.331964959974965</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.565015403727103</v>
+        <v>3.830946950386405</v>
       </c>
     </row>
   </sheetData>
